--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734427</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129734111</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734204</v>
+        <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>91584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,43 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574096</v>
+        <v>574081</v>
       </c>
       <c r="R4" t="n">
-        <v>7056877</v>
+        <v>7056834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129734349</v>
+        <v>129734204</v>
       </c>
       <c r="B5" t="n">
-        <v>91583</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574081</v>
+        <v>574096</v>
       </c>
       <c r="R5" t="n">
-        <v>7056834</v>
+        <v>7056877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734349</v>
+        <v>129734204</v>
       </c>
       <c r="B4" t="n">
-        <v>91584</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +920,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574081</v>
+        <v>574096</v>
       </c>
       <c r="R4" t="n">
-        <v>7056834</v>
+        <v>7056877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129734204</v>
+        <v>129734349</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>91584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574096</v>
+        <v>574081</v>
       </c>
       <c r="R5" t="n">
-        <v>7056877</v>
+        <v>7056834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734204</v>
+        <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>91589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,43 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574096</v>
+        <v>574081</v>
       </c>
       <c r="R4" t="n">
-        <v>7056877</v>
+        <v>7056834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129734349</v>
+        <v>129734204</v>
       </c>
       <c r="B5" t="n">
-        <v>91584</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574081</v>
+        <v>574096</v>
       </c>
       <c r="R5" t="n">
-        <v>7056834</v>
+        <v>7056877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734349</v>
+        <v>129734204</v>
       </c>
       <c r="B4" t="n">
-        <v>91595</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +920,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574081</v>
+        <v>574096</v>
       </c>
       <c r="R4" t="n">
-        <v>7056834</v>
+        <v>7056877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129734204</v>
+        <v>129734349</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>91595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574096</v>
+        <v>574081</v>
       </c>
       <c r="R5" t="n">
-        <v>7056877</v>
+        <v>7056834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734427</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129734111</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734204</v>
+        <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>91598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,43 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574096</v>
+        <v>574081</v>
       </c>
       <c r="R4" t="n">
-        <v>7056877</v>
+        <v>7056834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129734349</v>
+        <v>129734204</v>
       </c>
       <c r="B5" t="n">
-        <v>91595</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574081</v>
+        <v>574096</v>
       </c>
       <c r="R5" t="n">
-        <v>7056834</v>
+        <v>7056877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734349</v>
+        <v>129734204</v>
       </c>
       <c r="B4" t="n">
-        <v>91598</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +920,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574081</v>
+        <v>574096</v>
       </c>
       <c r="R4" t="n">
-        <v>7056834</v>
+        <v>7056877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129734204</v>
+        <v>129734349</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>91598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574096</v>
+        <v>574081</v>
       </c>
       <c r="R5" t="n">
-        <v>7056877</v>
+        <v>7056834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129734427</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129734111</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129734204</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>129734349</v>
       </c>
       <c r="B5" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734204</v>
+        <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>91601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,43 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574096</v>
+        <v>574081</v>
       </c>
       <c r="R4" t="n">
-        <v>7056877</v>
+        <v>7056834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129734349</v>
+        <v>129734204</v>
       </c>
       <c r="B5" t="n">
-        <v>91601</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574081</v>
+        <v>574096</v>
       </c>
       <c r="R5" t="n">
-        <v>7056834</v>
+        <v>7056877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129734349</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129734204</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55125-2025 artfynd.xlsx
+++ b/artfynd/A 55125-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129734427</v>
+        <v>129734349</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574074</v>
+        <v>574081</v>
       </c>
       <c r="R2" t="n">
-        <v>7056837</v>
+        <v>7056834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +785,7 @@
         <v>129734111</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129734349</v>
+        <v>129734427</v>
       </c>
       <c r="B4" t="n">
-        <v>91634</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574081</v>
+        <v>574074</v>
       </c>
       <c r="R4" t="n">
-        <v>7056834</v>
+        <v>7056837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1019,7 @@
         <v>129734204</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
